--- a/Output/Plantilla_Jugador.xlsx
+++ b/Output/Plantilla_Jugador.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reglas del Juego" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +26,30 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +57,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00808080"/>
+      </left>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -415,1987 +454,2071 @@
   </sheetPr>
   <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id_partido</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>local</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>visitante</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>goles_local</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>goles_visitante</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Mexico</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Czechia</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>South Africa</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Mexico</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Czechia</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>South Africa</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>South Africa</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Mexico</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Czechia</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Qatar</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Bosnia &amp; Herzegovina</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Qatar</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="F10" s="3" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Bosnia &amp; Herzegovina</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Bosnia &amp; Herzegovina</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr"/>
+      <c r="G12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Qatar</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Morocco</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr"/>
+      <c r="G14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Haiti</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Scotland</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr"/>
+      <c r="G15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Haiti</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="F16" s="3" t="inlineStr"/>
+      <c r="G16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Scotland</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Morocco</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="n">
+      <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Scotland</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+      <c r="F18" s="3" t="inlineStr"/>
+      <c r="G18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="n">
+      <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Morocco</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Haiti</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="n">
+      <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Turkey</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="n">
+      <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="n">
+      <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="F22" s="3" t="inlineStr"/>
+      <c r="G22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="n">
+      <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Turkey</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr"/>
+      <c r="G23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="n">
+      <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+      <c r="F24" s="3" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="n">
+      <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Turkey</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="n">
+      <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+      <c r="F26" s="3" t="inlineStr"/>
+      <c r="G26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="n">
+      <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Ivory Coast</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Curacao</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+      <c r="F27" s="3" t="inlineStr"/>
+      <c r="G27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="n">
+      <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Ivory Coast</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
+      <c r="F28" s="3" t="inlineStr"/>
+      <c r="G28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="n">
+      <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Curacao</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr"/>
+      <c r="G29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="n">
+      <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Curacao</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+      <c r="F30" s="3" t="inlineStr"/>
+      <c r="G30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="n">
+      <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Ivory Coast</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
+      <c r="F31" s="3" t="inlineStr"/>
+      <c r="G31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="n">
+      <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
+      <c r="F32" s="3" t="inlineStr"/>
+      <c r="G32" s="3" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="n">
+      <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Sweden</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Tunisia</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
+      <c r="F33" s="3" t="inlineStr"/>
+      <c r="G33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="n">
+      <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Sweden</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
+      <c r="F34" s="3" t="inlineStr"/>
+      <c r="G34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="n">
+      <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Tunisia</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
+      <c r="F35" s="3" t="inlineStr"/>
+      <c r="G35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="n">
+      <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Tunisia</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
+      <c r="F36" s="3" t="inlineStr"/>
+      <c r="G36" s="3" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="n">
+      <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Sweden</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
+      <c r="F37" s="3" t="inlineStr"/>
+      <c r="G37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="n">
+      <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Belgium</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Egypt</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
+      <c r="F38" s="3" t="inlineStr"/>
+      <c r="G38" s="3" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="n">
+      <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Iran</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>New Zealand</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
+      <c r="F39" s="3" t="inlineStr"/>
+      <c r="G39" s="3" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="n">
+      <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Belgium</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Iran</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
+      <c r="F40" s="3" t="inlineStr"/>
+      <c r="G40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="n">
+      <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>New Zealand</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Egypt</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
+      <c r="F41" s="3" t="inlineStr"/>
+      <c r="G41" s="3" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="n">
+      <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>26/06/2026</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>New Zealand</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Belgium</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
+      <c r="F42" s="3" t="inlineStr"/>
+      <c r="G42" s="3" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="n">
+      <c r="A43" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>26/06/2026</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Egypt</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Iran</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
+      <c r="F43" s="3" t="inlineStr"/>
+      <c r="G43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" t="n">
+      <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Cape Verde</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
+      <c r="F44" s="3" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="n">
+      <c r="A45" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Uruguay</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
+      <c r="F45" s="3" t="inlineStr"/>
+      <c r="G45" s="3" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="n">
+      <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
+      <c r="F46" s="3" t="inlineStr"/>
+      <c r="G46" s="3" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="n">
+      <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Uruguay</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Cape Verde</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
+      <c r="F47" s="3" t="inlineStr"/>
+      <c r="G47" s="3" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" t="n">
+      <c r="A48" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>26/06/2026</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Uruguay</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
+      <c r="F48" s="3" t="inlineStr"/>
+      <c r="G48" s="3" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="n">
+      <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>26/06/2026</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Cape Verde</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
+      <c r="F49" s="3" t="inlineStr"/>
+      <c r="G49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" t="n">
+      <c r="A50" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Senegal</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
+      <c r="F50" s="3" t="inlineStr"/>
+      <c r="G50" s="3" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" t="n">
+      <c r="A51" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Iraq</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
+      <c r="F51" s="3" t="inlineStr"/>
+      <c r="G51" s="3" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" t="n">
+      <c r="A52" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Iraq</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
+      <c r="F52" s="3" t="inlineStr"/>
+      <c r="G52" s="3" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" t="n">
+      <c r="A53" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Senegal</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
+      <c r="F53" s="3" t="inlineStr"/>
+      <c r="G53" s="3" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" t="n">
+      <c r="A54" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>26/06/2026</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
+      <c r="F54" s="3" t="inlineStr"/>
+      <c r="G54" s="3" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" t="n">
+      <c r="A55" s="2" t="n">
         <v>54</v>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>26/06/2026</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Senegal</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Iraq</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
+      <c r="F55" s="3" t="inlineStr"/>
+      <c r="G55" s="3" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" t="n">
+      <c r="A56" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Argentina</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Algeria</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
+      <c r="F56" s="3" t="inlineStr"/>
+      <c r="G56" s="3" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" t="n">
+      <c r="A57" s="2" t="n">
         <v>56</v>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Austria</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Jordan</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
+      <c r="F57" s="3" t="inlineStr"/>
+      <c r="G57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" t="n">
+      <c r="A58" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Argentina</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Austria</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
+      <c r="F58" s="3" t="inlineStr"/>
+      <c r="G58" s="3" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="n">
+      <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Jordan</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Algeria</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
+      <c r="F59" s="3" t="inlineStr"/>
+      <c r="G59" s="3" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" t="n">
+      <c r="A60" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>27/06/2026</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Jordan</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Argentina</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
+      <c r="F60" s="3" t="inlineStr"/>
+      <c r="G60" s="3" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" t="n">
+      <c r="A61" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>27/06/2026</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Algeria</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Austria</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
+      <c r="F61" s="3" t="inlineStr"/>
+      <c r="G61" s="3" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="n">
+      <c r="A62" s="2" t="n">
         <v>61</v>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>DR Congo</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
+      <c r="F62" s="3" t="inlineStr"/>
+      <c r="G62" s="3" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" t="n">
+      <c r="A63" s="2" t="n">
         <v>62</v>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Uzbekistan</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
+      <c r="F63" s="3" t="inlineStr"/>
+      <c r="G63" s="3" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="n">
+      <c r="A64" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Uzbekistan</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
+      <c r="F64" s="3" t="inlineStr"/>
+      <c r="G64" s="3" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" t="n">
+      <c r="A65" s="2" t="n">
         <v>64</v>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>DR Congo</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
+      <c r="F65" s="3" t="inlineStr"/>
+      <c r="G65" s="3" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" t="n">
+      <c r="A66" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>27/06/2026</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
+      <c r="F66" s="3" t="inlineStr"/>
+      <c r="G66" s="3" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" t="n">
+      <c r="A67" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>27/06/2026</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>DR Congo</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Uzbekistan</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
+      <c r="F67" s="3" t="inlineStr"/>
+      <c r="G67" s="3" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" t="n">
+      <c r="A68" s="2" t="n">
         <v>67</v>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Croatia</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
+      <c r="F68" s="3" t="inlineStr"/>
+      <c r="G68" s="3" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" t="n">
+      <c r="A69" s="2" t="n">
         <v>68</v>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Panama</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
+      <c r="F69" s="3" t="inlineStr"/>
+      <c r="G69" s="3" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" t="n">
+      <c r="A70" s="2" t="n">
         <v>69</v>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
+      <c r="F70" s="3" t="inlineStr"/>
+      <c r="G70" s="3" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" t="n">
+      <c r="A71" s="2" t="n">
         <v>70</v>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Panama</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Croatia</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
+      <c r="F71" s="3" t="inlineStr"/>
+      <c r="G71" s="3" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" t="n">
+      <c r="A72" s="2" t="n">
         <v>71</v>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>27/06/2026</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Panama</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
+      <c r="F72" s="3" t="inlineStr"/>
+      <c r="G72" s="3" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" t="n">
+      <c r="A73" s="2" t="n">
         <v>72</v>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>27/06/2026</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Croatia</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
+      <c r="F73" s="3" t="inlineStr"/>
+      <c r="G73" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="80" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>TotoGolFamiliar 2026 - Reglas del Juego</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Marcador exacto: 5 puntos</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Resultado correcto: 3 puntos</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Predicción incorrecta: 0 puntos</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Completa únicamente las columnas goles_local y goles_visitante.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Fecha límite de entrega:</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>10 de junio a las 12:00 mediodía.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
